--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_10d/rsi_10_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_10d/rsi_10_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -471,9 +471,9 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
@@ -560,43 +560,43 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-0.01481868751097715</v>
+        <v>0.03483081349940265</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>-0.02176047699359285</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.007096206316915321</v>
+        <v>0.05785013706977815</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.3099482698343762</v>
+        <v>0.2656974597654118</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.278089016680344</v>
+        <v>0.2609629985447763</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.0518464753046256</v>
+        <v>0.2218095365339208</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.07412259136996702</v>
+        <v>0.323764141373671</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.1426943674242865</v>
+        <v>0.3163139673987415</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.2274205193639005</v>
+        <v>0.1780876334408704</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.1506490308477421</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.2194284971135534</v>
+        <v>0.1882835245745039</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>-0.07356229895864154</v>
+        <v>0.2215125057394027</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>18.37110567373472</v>
+        <v>13.51919569327447</v>
       </c>
     </row>
     <row r="3">
@@ -606,43 +606,43 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.2203241531606223</v>
+        <v>-0.1498018109031664</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-0.2255774308756096</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.006783477037512808</v>
+        <v>0.09784789725087761</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.2103321892419232</v>
+        <v>0.1929768590454491</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.1963829522661493</v>
+        <v>0.1884730502100115</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-1.197577774103</v>
+        <v>-0.8563062076091973</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-1.627193463261388</v>
+        <v>-1.159237065913971</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.03760298585449239</v>
+        <v>0.4988854266451673</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.2551817189258342</v>
+        <v>0.2002900052545314</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.2845881262232945</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1576705273621674</v>
+        <v>0.1146510401028025</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-0.8946619952605309</v>
+        <v>-0.7762952835633865</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>14.93812259001251</v>
+        <v>11.52819109853204</v>
       </c>
     </row>
     <row r="4">
@@ -652,43 +652,43 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.1103870656736474</v>
+        <v>-0.1500678197487756</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-0.1141699148043651</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.004270400378060257</v>
+        <v>-0.04052459443899137</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.2590063692999576</v>
+        <v>0.157953195801825</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2357702963685437</v>
+        <v>0.1384885147356038</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.3992528756521546</v>
+        <v>-1.0869290753929</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.5921663063912612</v>
+        <v>-1.44879687075209</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.121174609371157</v>
+        <v>-0.2867061562832346</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.2722258153807793</v>
+        <v>0.2093092544462742</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.2177913835362562</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.1538170423683834</v>
+        <v>0.07930268676195729</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-0.4212552933106939</v>
+        <v>-0.7441588507076667</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>17.37926023585686</v>
+        <v>12.22598558071301</v>
       </c>
     </row>
     <row r="5">
@@ -698,43 +698,43 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.1103164732022692</v>
+        <v>-0.01815947982756771</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0.1298071537204202</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.2125350562102306</v>
+        <v>-0.1309662742537424</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.2260250574905078</v>
+        <v>0.1919839302998337</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.165985580087928</v>
+        <v>0.1516988713469889</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.4917638901097982</v>
+        <v>-0.08206992164463102</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.6953308180154577</v>
+        <v>-0.1250595446029491</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-1.500165595590146</v>
+        <v>-1.012604773067378</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.2332243938270515</v>
+        <v>0.1897335433034676</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.1515696200238076</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.3118137012723126</v>
+        <v>0.2300626585677132</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-0.4913868941154259</v>
+        <v>-0.09962779790662135</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>16.56235481694381</v>
+        <v>12.7447131229564</v>
       </c>
     </row>
     <row r="6">
@@ -744,43 +744,43 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.4495519599491025</v>
+        <v>0.08008515717702536</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.2243203183030871</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.1839646359526148</v>
+        <v>-0.1178083537206775</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.3383379160995386</v>
+        <v>0.1735027613100078</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.250075190269765</v>
+        <v>0.1180374293069942</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.263410921855405</v>
+        <v>0.4615468414332295</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.89613371701369</v>
+        <v>0.6260745303167955</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.8730954062214061</v>
+        <v>-1.093218210007688</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.2243522445160976</v>
+        <v>0.1158894640231911</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0.1188658802983931</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1973100817227643</v>
+        <v>0.1848396733948227</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.093231580378027</v>
+        <v>0.7176786715229553</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>18.25462556224468</v>
+        <v>13.72176274364882</v>
       </c>
     </row>
     <row r="7">
@@ -790,43 +790,43 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.05197520577914849</v>
+        <v>0.1303939225967012</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-0.01504143451691176</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.06804006040923172</v>
+        <v>0.1476563199816241</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.434597277303161</v>
+        <v>0.3007122669447543</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.3650546482670666</v>
+        <v>0.2703090595119821</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.3960016942442413</v>
+        <v>0.8452332455043806</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.547435901863692</v>
+        <v>1.18542883049647</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.5161556651262666</v>
+        <v>1.000690737109538</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.2422600485223561</v>
+        <v>0.1443412437138663</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.127969093077366</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.2311871066242884</v>
+        <v>0.1147462578854316</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.4001598890727191</v>
+        <v>1.737836371162803</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>19.25536280511705</v>
+        <v>14.02283658791556</v>
       </c>
     </row>
   </sheetData>
